--- a/tests/mung/fixtures/sumprod_z2_2026-07-06.xlsx
+++ b/tests/mung/fixtures/sumprod_z2_2026-07-06.xlsx
@@ -12,14 +12,13 @@
     <sheet name="incomplete" sheetId="3" r:id="rId3"/>
     <sheet name="incomplete_uniq" sheetId="4" r:id="rId4"/>
     <sheet name="calc" sheetId="5" r:id="rId5"/>
-    <sheet name="calc_aug" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="44">
   <si>
     <t>entity</t>
   </si>
@@ -269,21 +268,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Frame4" displayName="Frame4" ref="A1:E14" totalsRowShown="0">
-  <autoFilter ref="A1:E14"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="entity" dataDxfId="0"/>
-    <tableColumn id="2" name="period" dataDxfId="0"/>
-    <tableColumn id="3" name="pertype" dataDxfId="0"/>
-    <tableColumn id="4" name="concept" dataDxfId="0"/>
-    <tableColumn id="5" name="adds_amt" dataDxfId="1"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Frame5" displayName="Frame5" ref="A1:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Frame4" displayName="Frame4" ref="A1:F14" totalsRowShown="0">
   <autoFilter ref="A1:F14"/>
   <tableColumns count="6">
     <tableColumn id="1" name="entity" dataDxfId="0"/>
@@ -1480,13 +1465,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1503,13 +1488,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1687,10 +1672,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
@@ -1716,7 +1701,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1733,10 +1718,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>8</v>
@@ -1756,13 +1741,13 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1782,7 +1767,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>8</v>
@@ -1808,7 +1793,7 @@
         <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1851,7 +1836,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>8</v>
@@ -1871,10 +1856,10 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>8</v>
@@ -1894,13 +1879,13 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1917,10 +1902,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>8</v>
@@ -1940,10 +1925,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>8</v>
@@ -1989,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>8</v>
@@ -2009,13 +1994,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2038,7 +2023,7 @@
         <v>17</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2055,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>8</v>
@@ -2078,10 +2063,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>8</v>
@@ -2101,13 +2086,13 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2124,13 +2109,13 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2147,13 +2132,13 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2173,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>8</v>
@@ -2193,13 +2178,13 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2216,13 +2201,13 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2239,10 +2224,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>8</v>
@@ -2265,7 +2250,7 @@
         <v>6</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>8</v>
@@ -2285,13 +2270,13 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2308,13 +2293,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2331,13 +2316,13 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2354,13 +2339,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2380,7 +2365,7 @@
         <v>6</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>8</v>
@@ -2400,13 +2385,13 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2423,10 +2408,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>8</v>
@@ -2446,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2469,13 +2454,13 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2492,10 +2477,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>8</v>
@@ -2515,13 +2500,13 @@
         <v>1</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2538,13 +2523,13 @@
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2564,7 +2549,7 @@
         <v>6</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>8</v>
@@ -2584,13 +2569,13 @@
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2607,13 +2592,13 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2630,13 +2615,13 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2653,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>7</v>
@@ -2676,10 +2661,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>8</v>
@@ -2705,7 +2690,7 @@
         <v>17</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2745,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>17</v>
@@ -2768,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2791,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>17</v>
@@ -2814,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>7</v>
@@ -2860,10 +2845,10 @@
         <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>8</v>
@@ -2889,7 +2874,7 @@
         <v>17</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2912,7 +2897,7 @@
         <v>17</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2929,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>17</v>
@@ -2952,13 +2937,13 @@
         <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2975,10 +2960,10 @@
         <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>8</v>
@@ -3021,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>7</v>
@@ -3044,10 +3029,10 @@
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>8</v>
@@ -3067,13 +3052,13 @@
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3113,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>7</v>
@@ -3142,7 +3127,7 @@
         <v>17</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3159,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>17</v>
@@ -3182,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>17</v>
@@ -3205,13 +3190,13 @@
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3234,7 +3219,7 @@
         <v>17</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3251,13 +3236,13 @@
         <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3274,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>17</v>
@@ -3303,7 +3288,7 @@
         <v>17</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3369,10 +3354,10 @@
         <v>6</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3389,10 +3374,10 @@
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>8</v>
@@ -3412,13 +3397,13 @@
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3507,10 +3492,10 @@
         <v>6</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3550,13 +3535,13 @@
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3573,10 +3558,10 @@
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>8</v>
@@ -3599,10 +3584,10 @@
         <v>6</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3619,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>17</v>
@@ -3645,10 +3630,10 @@
         <v>6</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3665,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>8</v>
@@ -3688,13 +3673,13 @@
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3711,13 +3696,13 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3734,10 +3719,10 @@
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>8</v>
@@ -3757,13 +3742,13 @@
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3806,10 +3791,10 @@
         <v>6</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3918,13 +3903,13 @@
         <v>-1</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3941,13 +3926,13 @@
         <v>-1</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3964,13 +3949,13 @@
         <v>-1</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3987,13 +3972,13 @@
         <v>-1</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4010,7 +3995,7 @@
         <v>-1</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>17</v>
@@ -4033,7 +4018,7 @@
         <v>-1</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>17</v>
@@ -4079,10 +4064,10 @@
         <v>-1</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>8</v>
@@ -4102,7 +4087,7 @@
         <v>-1</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>17</v>
@@ -4125,10 +4110,10 @@
         <v>-1</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>8</v>
@@ -4148,13 +4133,13 @@
         <v>-1</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4171,13 +4156,13 @@
         <v>-1</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4209,41 +4194,41 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>32</v>
@@ -4251,7 +4236,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>17</v>
@@ -4260,12 +4245,12 @@
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -4274,7 +4259,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4288,7 +4273,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4299,7 +4284,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>26</v>
@@ -4313,15 +4298,15 @@
         <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -4335,7 +4320,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -4344,15 +4329,15 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
@@ -4372,7 +4357,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4386,43 +4371,43 @@
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>8</v>
@@ -4439,15 +4424,15 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>17</v>
@@ -4456,7 +4441,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4467,15 +4452,15 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -4484,7 +4469,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4498,7 +4483,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4506,10 +4491,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>30</v>
@@ -4517,13 +4502,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>15</v>
@@ -4537,10 +4522,10 @@
         <v>17</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4551,15 +4536,15 @@
         <v>17</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -4568,7 +4553,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4579,24 +4564,24 @@
         <v>17</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4607,32 +4592,32 @@
         <v>17</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>8</v>
@@ -4646,41 +4631,41 @@
         <v>6</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -4688,24 +4673,24 @@
         <v>6</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>35</v>
@@ -4721,257 +4706,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="2">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="2">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="2">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="2">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="2">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
